--- a/tools/candidates/s1-oplata-za-raboty/08-uchet-obemov-peredachi-raschetov.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/08-uchet-obemov-peredachi-raschetov.xlsx
@@ -30693,7 +30693,7 @@
         <v/>
       </c>
       <c r="H5" s="9">
-        <f>IF(OR(B5="",E5=""),"",F5-G5)</f>
+        <f>IF(OR(B5="",E5=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F5-G5))</f>
         <v/>
       </c>
       <c r="I5" s="9">
@@ -30701,11 +30701,11 @@
         <v/>
       </c>
       <c r="J5" s="9">
-        <f>IF(OR(B5="",E5=""),"",H5-I5)</f>
+        <f>IF(OR(B5="",E5=""),"",IF(NOT(ISNUMBER(H5)),"ЗАБЛОКИРОВАН",H5-I5))</f>
         <v/>
       </c>
       <c r="K5" s="5">
-        <f>IF(AND(B5="",C5="",D5=""),"",IF(B5="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B5)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D5)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B5)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H5)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J5)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B5="",C5="",D5=""),"",IF(B5="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B5)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D5)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B5)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H5)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J5)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L5" s="5">
@@ -30742,7 +30742,7 @@
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>IF(OR(B6="",E6=""),"",F6-G6)</f>
+        <f>IF(OR(B6="",E6=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F6-G6))</f>
         <v/>
       </c>
       <c r="I6" s="9">
@@ -30750,11 +30750,11 @@
         <v/>
       </c>
       <c r="J6" s="9">
-        <f>IF(OR(B6="",E6=""),"",H6-I6)</f>
+        <f>IF(OR(B6="",E6=""),"",IF(NOT(ISNUMBER(H6)),"ЗАБЛОКИРОВАН",H6-I6))</f>
         <v/>
       </c>
       <c r="K6" s="5">
-        <f>IF(AND(B6="",C6="",D6=""),"",IF(B6="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B6)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D6)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B6)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H6)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J6)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B6="",C6="",D6=""),"",IF(B6="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B6)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D6)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B6)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H6)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J6)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L6" s="5">
@@ -30791,7 +30791,7 @@
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>IF(OR(B7="",E7=""),"",F7-G7)</f>
+        <f>IF(OR(B7="",E7=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F7-G7))</f>
         <v/>
       </c>
       <c r="I7" s="9">
@@ -30799,11 +30799,11 @@
         <v/>
       </c>
       <c r="J7" s="9">
-        <f>IF(OR(B7="",E7=""),"",H7-I7)</f>
+        <f>IF(OR(B7="",E7=""),"",IF(NOT(ISNUMBER(H7)),"ЗАБЛОКИРОВАН",H7-I7))</f>
         <v/>
       </c>
       <c r="K7" s="5">
-        <f>IF(AND(B7="",C7="",D7=""),"",IF(B7="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B7)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D7)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B7)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H7)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J7)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B7="",C7="",D7=""),"",IF(B7="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B7)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D7)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B7)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H7)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J7)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L7" s="5">
@@ -30840,7 +30840,7 @@
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IF(OR(B8="",E8=""),"",F8-G8)</f>
+        <f>IF(OR(B8="",E8=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F8-G8))</f>
         <v/>
       </c>
       <c r="I8" s="9">
@@ -30848,11 +30848,11 @@
         <v/>
       </c>
       <c r="J8" s="9">
-        <f>IF(OR(B8="",E8=""),"",H8-I8)</f>
+        <f>IF(OR(B8="",E8=""),"",IF(NOT(ISNUMBER(H8)),"ЗАБЛОКИРОВАН",H8-I8))</f>
         <v/>
       </c>
       <c r="K8" s="5">
-        <f>IF(AND(B8="",C8="",D8=""),"",IF(B8="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B8)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D8)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B8)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H8)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J8)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B8="",C8="",D8=""),"",IF(B8="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B8)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D8)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B8)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H8)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J8)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L8" s="5">
@@ -30889,7 +30889,7 @@
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IF(OR(B9="",E9=""),"",F9-G9)</f>
+        <f>IF(OR(B9="",E9=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F9-G9))</f>
         <v/>
       </c>
       <c r="I9" s="9">
@@ -30897,11 +30897,11 @@
         <v/>
       </c>
       <c r="J9" s="9">
-        <f>IF(OR(B9="",E9=""),"",H9-I9)</f>
+        <f>IF(OR(B9="",E9=""),"",IF(NOT(ISNUMBER(H9)),"ЗАБЛОКИРОВАН",H9-I9))</f>
         <v/>
       </c>
       <c r="K9" s="5">
-        <f>IF(AND(B9="",C9="",D9=""),"",IF(B9="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B9)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D9)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B9)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H9)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J9)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B9="",C9="",D9=""),"",IF(B9="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B9)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D9)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B9)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H9)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J9)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L9" s="5">
@@ -30929,7 +30929,7 @@
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IF(OR(B10="",E10=""),"",F10-G10)</f>
+        <f>IF(OR(B10="",E10=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F10-G10))</f>
         <v/>
       </c>
       <c r="I10" s="9">
@@ -30937,11 +30937,11 @@
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>IF(OR(B10="",E10=""),"",H10-I10)</f>
+        <f>IF(OR(B10="",E10=""),"",IF(NOT(ISNUMBER(H10)),"ЗАБЛОКИРОВАН",H10-I10))</f>
         <v/>
       </c>
       <c r="K10" s="5">
-        <f>IF(AND(B10="",C10="",D10=""),"",IF(B10="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B10)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D10)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B10)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H10)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J10)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B10="",C10="",D10=""),"",IF(B10="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B10)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D10)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B10)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H10)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J10)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L10" s="5">
@@ -30969,7 +30969,7 @@
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IF(OR(B11="",E11=""),"",F11-G11)</f>
+        <f>IF(OR(B11="",E11=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F11-G11))</f>
         <v/>
       </c>
       <c r="I11" s="9">
@@ -30977,11 +30977,11 @@
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>IF(OR(B11="",E11=""),"",H11-I11)</f>
+        <f>IF(OR(B11="",E11=""),"",IF(NOT(ISNUMBER(H11)),"ЗАБЛОКИРОВАН",H11-I11))</f>
         <v/>
       </c>
       <c r="K11" s="5">
-        <f>IF(AND(B11="",C11="",D11=""),"",IF(B11="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B11)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D11)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B11)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H11)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J11)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B11="",C11="",D11=""),"",IF(B11="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B11)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D11)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B11)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H11)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J11)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L11" s="5">
@@ -31009,7 +31009,7 @@
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IF(OR(B12="",E12=""),"",F12-G12)</f>
+        <f>IF(OR(B12="",E12=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F12-G12))</f>
         <v/>
       </c>
       <c r="I12" s="9">
@@ -31017,11 +31017,11 @@
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>IF(OR(B12="",E12=""),"",H12-I12)</f>
+        <f>IF(OR(B12="",E12=""),"",IF(NOT(ISNUMBER(H12)),"ЗАБЛОКИРОВАН",H12-I12))</f>
         <v/>
       </c>
       <c r="K12" s="5">
-        <f>IF(AND(B12="",C12="",D12=""),"",IF(B12="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B12)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D12)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B12)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H12)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J12)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B12="",C12="",D12=""),"",IF(B12="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B12)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D12)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B12)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H12)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J12)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L12" s="5">
@@ -31049,7 +31049,7 @@
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IF(OR(B13="",E13=""),"",F13-G13)</f>
+        <f>IF(OR(B13="",E13=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F13-G13))</f>
         <v/>
       </c>
       <c r="I13" s="9">
@@ -31057,11 +31057,11 @@
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>IF(OR(B13="",E13=""),"",H13-I13)</f>
+        <f>IF(OR(B13="",E13=""),"",IF(NOT(ISNUMBER(H13)),"ЗАБЛОКИРОВАН",H13-I13))</f>
         <v/>
       </c>
       <c r="K13" s="5">
-        <f>IF(AND(B13="",C13="",D13=""),"",IF(B13="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B13)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D13)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B13)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H13)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J13)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B13="",C13="",D13=""),"",IF(B13="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B13)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D13)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B13)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H13)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J13)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L13" s="5">
@@ -31089,7 +31089,7 @@
         <v/>
       </c>
       <c r="H14" s="9">
-        <f>IF(OR(B14="",E14=""),"",F14-G14)</f>
+        <f>IF(OR(B14="",E14=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F14-G14))</f>
         <v/>
       </c>
       <c r="I14" s="9">
@@ -31097,11 +31097,11 @@
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>IF(OR(B14="",E14=""),"",H14-I14)</f>
+        <f>IF(OR(B14="",E14=""),"",IF(NOT(ISNUMBER(H14)),"ЗАБЛОКИРОВАН",H14-I14))</f>
         <v/>
       </c>
       <c r="K14" s="5">
-        <f>IF(AND(B14="",C14="",D14=""),"",IF(B14="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B14)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D14)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B14)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H14)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J14)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B14="",C14="",D14=""),"",IF(B14="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B14)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D14)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B14)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H14)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J14)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L14" s="5">
@@ -31129,7 +31129,7 @@
         <v/>
       </c>
       <c r="H15" s="9">
-        <f>IF(OR(B15="",E15=""),"",F15-G15)</f>
+        <f>IF(OR(B15="",E15=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F15-G15))</f>
         <v/>
       </c>
       <c r="I15" s="9">
@@ -31137,11 +31137,11 @@
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>IF(OR(B15="",E15=""),"",H15-I15)</f>
+        <f>IF(OR(B15="",E15=""),"",IF(NOT(ISNUMBER(H15)),"ЗАБЛОКИРОВАН",H15-I15))</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>IF(AND(B15="",C15="",D15=""),"",IF(B15="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B15)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D15)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B15)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H15)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J15)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B15="",C15="",D15=""),"",IF(B15="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B15)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D15)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B15)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H15)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J15)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L15" s="5">
@@ -31169,7 +31169,7 @@
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>IF(OR(B16="",E16=""),"",F16-G16)</f>
+        <f>IF(OR(B16="",E16=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F16-G16))</f>
         <v/>
       </c>
       <c r="I16" s="9">
@@ -31177,11 +31177,11 @@
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>IF(OR(B16="",E16=""),"",H16-I16)</f>
+        <f>IF(OR(B16="",E16=""),"",IF(NOT(ISNUMBER(H16)),"ЗАБЛОКИРОВАН",H16-I16))</f>
         <v/>
       </c>
       <c r="K16" s="5">
-        <f>IF(AND(B16="",C16="",D16=""),"",IF(B16="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B16)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D16)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B16)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H16)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J16)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B16="",C16="",D16=""),"",IF(B16="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B16)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D16)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B16)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H16)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J16)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L16" s="5">
@@ -31209,7 +31209,7 @@
         <v/>
       </c>
       <c r="H17" s="9">
-        <f>IF(OR(B17="",E17=""),"",F17-G17)</f>
+        <f>IF(OR(B17="",E17=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F17-G17))</f>
         <v/>
       </c>
       <c r="I17" s="9">
@@ -31217,11 +31217,11 @@
         <v/>
       </c>
       <c r="J17" s="9">
-        <f>IF(OR(B17="",E17=""),"",H17-I17)</f>
+        <f>IF(OR(B17="",E17=""),"",IF(NOT(ISNUMBER(H17)),"ЗАБЛОКИРОВАН",H17-I17))</f>
         <v/>
       </c>
       <c r="K17" s="5">
-        <f>IF(AND(B17="",C17="",D17=""),"",IF(B17="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B17)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D17)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B17)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H17)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J17)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B17="",C17="",D17=""),"",IF(B17="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B17)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D17)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B17)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H17)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J17)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L17" s="5">
@@ -31249,7 +31249,7 @@
         <v/>
       </c>
       <c r="H18" s="9">
-        <f>IF(OR(B18="",E18=""),"",F18-G18)</f>
+        <f>IF(OR(B18="",E18=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F18-G18))</f>
         <v/>
       </c>
       <c r="I18" s="9">
@@ -31257,11 +31257,11 @@
         <v/>
       </c>
       <c r="J18" s="9">
-        <f>IF(OR(B18="",E18=""),"",H18-I18)</f>
+        <f>IF(OR(B18="",E18=""),"",IF(NOT(ISNUMBER(H18)),"ЗАБЛОКИРОВАН",H18-I18))</f>
         <v/>
       </c>
       <c r="K18" s="5">
-        <f>IF(AND(B18="",C18="",D18=""),"",IF(B18="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B18)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D18)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B18)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H18)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J18)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B18="",C18="",D18=""),"",IF(B18="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B18)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D18)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B18)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H18)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J18)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L18" s="5">
@@ -31289,7 +31289,7 @@
         <v/>
       </c>
       <c r="H19" s="9">
-        <f>IF(OR(B19="",E19=""),"",F19-G19)</f>
+        <f>IF(OR(B19="",E19=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F19-G19))</f>
         <v/>
       </c>
       <c r="I19" s="9">
@@ -31297,11 +31297,11 @@
         <v/>
       </c>
       <c r="J19" s="9">
-        <f>IF(OR(B19="",E19=""),"",H19-I19)</f>
+        <f>IF(OR(B19="",E19=""),"",IF(NOT(ISNUMBER(H19)),"ЗАБЛОКИРОВАН",H19-I19))</f>
         <v/>
       </c>
       <c r="K19" s="5">
-        <f>IF(AND(B19="",C19="",D19=""),"",IF(B19="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B19)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D19)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B19)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H19)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J19)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B19="",C19="",D19=""),"",IF(B19="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B19)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D19)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B19)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H19)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J19)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L19" s="5">
@@ -31329,7 +31329,7 @@
         <v/>
       </c>
       <c r="H20" s="9">
-        <f>IF(OR(B20="",E20=""),"",F20-G20)</f>
+        <f>IF(OR(B20="",E20=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F20-G20))</f>
         <v/>
       </c>
       <c r="I20" s="9">
@@ -31337,11 +31337,11 @@
         <v/>
       </c>
       <c r="J20" s="9">
-        <f>IF(OR(B20="",E20=""),"",H20-I20)</f>
+        <f>IF(OR(B20="",E20=""),"",IF(NOT(ISNUMBER(H20)),"ЗАБЛОКИРОВАН",H20-I20))</f>
         <v/>
       </c>
       <c r="K20" s="5">
-        <f>IF(AND(B20="",C20="",D20=""),"",IF(B20="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B20)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D20)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B20)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H20)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J20)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B20="",C20="",D20=""),"",IF(B20="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B20)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D20)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B20)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H20)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J20)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L20" s="5">
@@ -31369,7 +31369,7 @@
         <v/>
       </c>
       <c r="H21" s="9">
-        <f>IF(OR(B21="",E21=""),"",F21-G21)</f>
+        <f>IF(OR(B21="",E21=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F21-G21))</f>
         <v/>
       </c>
       <c r="I21" s="9">
@@ -31377,11 +31377,11 @@
         <v/>
       </c>
       <c r="J21" s="9">
-        <f>IF(OR(B21="",E21=""),"",H21-I21)</f>
+        <f>IF(OR(B21="",E21=""),"",IF(NOT(ISNUMBER(H21)),"ЗАБЛОКИРОВАН",H21-I21))</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>IF(AND(B21="",C21="",D21=""),"",IF(B21="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B21)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D21)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B21)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H21)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J21)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B21="",C21="",D21=""),"",IF(B21="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B21)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D21)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B21)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H21)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J21)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L21" s="5">
@@ -31409,7 +31409,7 @@
         <v/>
       </c>
       <c r="H22" s="9">
-        <f>IF(OR(B22="",E22=""),"",F22-G22)</f>
+        <f>IF(OR(B22="",E22=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F22-G22))</f>
         <v/>
       </c>
       <c r="I22" s="9">
@@ -31417,11 +31417,11 @@
         <v/>
       </c>
       <c r="J22" s="9">
-        <f>IF(OR(B22="",E22=""),"",H22-I22)</f>
+        <f>IF(OR(B22="",E22=""),"",IF(NOT(ISNUMBER(H22)),"ЗАБЛОКИРОВАН",H22-I22))</f>
         <v/>
       </c>
       <c r="K22" s="5">
-        <f>IF(AND(B22="",C22="",D22=""),"",IF(B22="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B22)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D22)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B22)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H22)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J22)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B22="",C22="",D22=""),"",IF(B22="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B22)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D22)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B22)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H22)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J22)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L22" s="5">
@@ -31449,7 +31449,7 @@
         <v/>
       </c>
       <c r="H23" s="9">
-        <f>IF(OR(B23="",E23=""),"",F23-G23)</f>
+        <f>IF(OR(B23="",E23=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F23-G23))</f>
         <v/>
       </c>
       <c r="I23" s="9">
@@ -31457,11 +31457,11 @@
         <v/>
       </c>
       <c r="J23" s="9">
-        <f>IF(OR(B23="",E23=""),"",H23-I23)</f>
+        <f>IF(OR(B23="",E23=""),"",IF(NOT(ISNUMBER(H23)),"ЗАБЛОКИРОВАН",H23-I23))</f>
         <v/>
       </c>
       <c r="K23" s="5">
-        <f>IF(AND(B23="",C23="",D23=""),"",IF(B23="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B23)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D23)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B23)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H23)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J23)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B23="",C23="",D23=""),"",IF(B23="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B23)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D23)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B23)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H23)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J23)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L23" s="5">
@@ -31489,7 +31489,7 @@
         <v/>
       </c>
       <c r="H24" s="9">
-        <f>IF(OR(B24="",E24=""),"",F24-G24)</f>
+        <f>IF(OR(B24="",E24=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F24-G24))</f>
         <v/>
       </c>
       <c r="I24" s="9">
@@ -31497,11 +31497,11 @@
         <v/>
       </c>
       <c r="J24" s="9">
-        <f>IF(OR(B24="",E24=""),"",H24-I24)</f>
+        <f>IF(OR(B24="",E24=""),"",IF(NOT(ISNUMBER(H24)),"ЗАБЛОКИРОВАН",H24-I24))</f>
         <v/>
       </c>
       <c r="K24" s="5">
-        <f>IF(AND(B24="",C24="",D24=""),"",IF(B24="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B24)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D24)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B24)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H24)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J24)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B24="",C24="",D24=""),"",IF(B24="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B24)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D24)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B24)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H24)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J24)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L24" s="5">
@@ -31529,7 +31529,7 @@
         <v/>
       </c>
       <c r="H25" s="9">
-        <f>IF(OR(B25="",E25=""),"",F25-G25)</f>
+        <f>IF(OR(B25="",E25=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F25-G25))</f>
         <v/>
       </c>
       <c r="I25" s="9">
@@ -31537,11 +31537,11 @@
         <v/>
       </c>
       <c r="J25" s="9">
-        <f>IF(OR(B25="",E25=""),"",H25-I25)</f>
+        <f>IF(OR(B25="",E25=""),"",IF(NOT(ISNUMBER(H25)),"ЗАБЛОКИРОВАН",H25-I25))</f>
         <v/>
       </c>
       <c r="K25" s="5">
-        <f>IF(AND(B25="",C25="",D25=""),"",IF(B25="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B25)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D25)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B25)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H25)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J25)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B25="",C25="",D25=""),"",IF(B25="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B25)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D25)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B25)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H25)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J25)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L25" s="5">
@@ -31569,7 +31569,7 @@
         <v/>
       </c>
       <c r="H26" s="9">
-        <f>IF(OR(B26="",E26=""),"",F26-G26)</f>
+        <f>IF(OR(B26="",E26=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F26-G26))</f>
         <v/>
       </c>
       <c r="I26" s="9">
@@ -31577,11 +31577,11 @@
         <v/>
       </c>
       <c r="J26" s="9">
-        <f>IF(OR(B26="",E26=""),"",H26-I26)</f>
+        <f>IF(OR(B26="",E26=""),"",IF(NOT(ISNUMBER(H26)),"ЗАБЛОКИРОВАН",H26-I26))</f>
         <v/>
       </c>
       <c r="K26" s="5">
-        <f>IF(AND(B26="",C26="",D26=""),"",IF(B26="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B26)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D26)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B26)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H26)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J26)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B26="",C26="",D26=""),"",IF(B26="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B26)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D26)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B26)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H26)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J26)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L26" s="5">
@@ -31609,7 +31609,7 @@
         <v/>
       </c>
       <c r="H27" s="9">
-        <f>IF(OR(B27="",E27=""),"",F27-G27)</f>
+        <f>IF(OR(B27="",E27=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F27-G27))</f>
         <v/>
       </c>
       <c r="I27" s="9">
@@ -31617,11 +31617,11 @@
         <v/>
       </c>
       <c r="J27" s="9">
-        <f>IF(OR(B27="",E27=""),"",H27-I27)</f>
+        <f>IF(OR(B27="",E27=""),"",IF(NOT(ISNUMBER(H27)),"ЗАБЛОКИРОВАН",H27-I27))</f>
         <v/>
       </c>
       <c r="K27" s="5">
-        <f>IF(AND(B27="",C27="",D27=""),"",IF(B27="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B27)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D27)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B27)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H27)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J27)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B27="",C27="",D27=""),"",IF(B27="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B27)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D27)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B27)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H27)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J27)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L27" s="5">
@@ -31649,7 +31649,7 @@
         <v/>
       </c>
       <c r="H28" s="9">
-        <f>IF(OR(B28="",E28=""),"",F28-G28)</f>
+        <f>IF(OR(B28="",E28=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F28-G28))</f>
         <v/>
       </c>
       <c r="I28" s="9">
@@ -31657,11 +31657,11 @@
         <v/>
       </c>
       <c r="J28" s="9">
-        <f>IF(OR(B28="",E28=""),"",H28-I28)</f>
+        <f>IF(OR(B28="",E28=""),"",IF(NOT(ISNUMBER(H28)),"ЗАБЛОКИРОВАН",H28-I28))</f>
         <v/>
       </c>
       <c r="K28" s="5">
-        <f>IF(AND(B28="",C28="",D28=""),"",IF(B28="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B28)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D28)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B28)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H28)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J28)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B28="",C28="",D28=""),"",IF(B28="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B28)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D28)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B28)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H28)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J28)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L28" s="5">
@@ -31689,7 +31689,7 @@
         <v/>
       </c>
       <c r="H29" s="9">
-        <f>IF(OR(B29="",E29=""),"",F29-G29)</f>
+        <f>IF(OR(B29="",E29=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F29-G29))</f>
         <v/>
       </c>
       <c r="I29" s="9">
@@ -31697,11 +31697,11 @@
         <v/>
       </c>
       <c r="J29" s="9">
-        <f>IF(OR(B29="",E29=""),"",H29-I29)</f>
+        <f>IF(OR(B29="",E29=""),"",IF(NOT(ISNUMBER(H29)),"ЗАБЛОКИРОВАН",H29-I29))</f>
         <v/>
       </c>
       <c r="K29" s="5">
-        <f>IF(AND(B29="",C29="",D29=""),"",IF(B29="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B29)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D29)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B29)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H29)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J29)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B29="",C29="",D29=""),"",IF(B29="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B29)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D29)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B29)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H29)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J29)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L29" s="5">
@@ -31729,7 +31729,7 @@
         <v/>
       </c>
       <c r="H30" s="9">
-        <f>IF(OR(B30="",E30=""),"",F30-G30)</f>
+        <f>IF(OR(B30="",E30=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F30-G30))</f>
         <v/>
       </c>
       <c r="I30" s="9">
@@ -31737,11 +31737,11 @@
         <v/>
       </c>
       <c r="J30" s="9">
-        <f>IF(OR(B30="",E30=""),"",H30-I30)</f>
+        <f>IF(OR(B30="",E30=""),"",IF(NOT(ISNUMBER(H30)),"ЗАБЛОКИРОВАН",H30-I30))</f>
         <v/>
       </c>
       <c r="K30" s="5">
-        <f>IF(AND(B30="",C30="",D30=""),"",IF(B30="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B30)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D30)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B30)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H30)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J30)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B30="",C30="",D30=""),"",IF(B30="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B30)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D30)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B30)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H30)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J30)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L30" s="5">
@@ -31769,7 +31769,7 @@
         <v/>
       </c>
       <c r="H31" s="9">
-        <f>IF(OR(B31="",E31=""),"",F31-G31)</f>
+        <f>IF(OR(B31="",E31=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F31-G31))</f>
         <v/>
       </c>
       <c r="I31" s="9">
@@ -31777,11 +31777,11 @@
         <v/>
       </c>
       <c r="J31" s="9">
-        <f>IF(OR(B31="",E31=""),"",H31-I31)</f>
+        <f>IF(OR(B31="",E31=""),"",IF(NOT(ISNUMBER(H31)),"ЗАБЛОКИРОВАН",H31-I31))</f>
         <v/>
       </c>
       <c r="K31" s="5">
-        <f>IF(AND(B31="",C31="",D31=""),"",IF(B31="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B31)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D31)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B31)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H31)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J31)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B31="",C31="",D31=""),"",IF(B31="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B31)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D31)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B31)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H31)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J31)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L31" s="5">
@@ -31809,7 +31809,7 @@
         <v/>
       </c>
       <c r="H32" s="9">
-        <f>IF(OR(B32="",E32=""),"",F32-G32)</f>
+        <f>IF(OR(B32="",E32=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F32-G32))</f>
         <v/>
       </c>
       <c r="I32" s="9">
@@ -31817,11 +31817,11 @@
         <v/>
       </c>
       <c r="J32" s="9">
-        <f>IF(OR(B32="",E32=""),"",H32-I32)</f>
+        <f>IF(OR(B32="",E32=""),"",IF(NOT(ISNUMBER(H32)),"ЗАБЛОКИРОВАН",H32-I32))</f>
         <v/>
       </c>
       <c r="K32" s="5">
-        <f>IF(AND(B32="",C32="",D32=""),"",IF(B32="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B32)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D32)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B32)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H32)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J32)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B32="",C32="",D32=""),"",IF(B32="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B32)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D32)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B32)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H32)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J32)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L32" s="5">
@@ -31849,7 +31849,7 @@
         <v/>
       </c>
       <c r="H33" s="9">
-        <f>IF(OR(B33="",E33=""),"",F33-G33)</f>
+        <f>IF(OR(B33="",E33=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F33-G33))</f>
         <v/>
       </c>
       <c r="I33" s="9">
@@ -31857,11 +31857,11 @@
         <v/>
       </c>
       <c r="J33" s="9">
-        <f>IF(OR(B33="",E33=""),"",H33-I33)</f>
+        <f>IF(OR(B33="",E33=""),"",IF(NOT(ISNUMBER(H33)),"ЗАБЛОКИРОВАН",H33-I33))</f>
         <v/>
       </c>
       <c r="K33" s="5">
-        <f>IF(AND(B33="",C33="",D33=""),"",IF(B33="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B33)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D33)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B33)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H33)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J33)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B33="",C33="",D33=""),"",IF(B33="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B33)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D33)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B33)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H33)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J33)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L33" s="5">
@@ -31889,7 +31889,7 @@
         <v/>
       </c>
       <c r="H34" s="9">
-        <f>IF(OR(B34="",E34=""),"",F34-G34)</f>
+        <f>IF(OR(B34="",E34=""),"",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"ЗАБЛОКИРОВАН",F34-G34))</f>
         <v/>
       </c>
       <c r="I34" s="9">
@@ -31897,11 +31897,11 @@
         <v/>
       </c>
       <c r="J34" s="9">
-        <f>IF(OR(B34="",E34=""),"",H34-I34)</f>
+        <f>IF(OR(B34="",E34=""),"",IF(NOT(ISNUMBER(H34)),"ЗАБЛОКИРОВАН",H34-I34))</f>
         <v/>
       </c>
       <c r="K34" s="5">
-        <f>IF(AND(B34="",C34="",D34=""),"",IF(B34="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B34)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D34)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B34)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(N(H34)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J34)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок")))))))</f>
+        <f>IF(AND(B34="",C34="",D34=""),"",IF(B34="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B34)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D34)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B34)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 14 не переносится",IF(N(H34)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J34)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
         <v/>
       </c>
       <c r="L34" s="5">
